--- a/mri-data/roi-time-courses/roi02c_stats_glm001_onset_O3_4to10_subpeaks.xlsx
+++ b/mri-data/roi-time-courses/roi02c_stats_glm001_onset_O3_4to10_subpeaks.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="140" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="315" uniqueCount="6">
   <si>
     <t>SMG_left_centr_765154</t>
   </si>
@@ -102,10 +102,10 @@
     </row>
     <row r="2">
       <c r="A2" s="0">
-        <v>0.57280731521729644</v>
+        <v>0.064001685563599767</v>
       </c>
       <c r="B2" s="0">
-        <v>-0.43641697410460262</v>
+        <v>-0.046313216185587584</v>
       </c>
       <c r="C2" s="0">
         <v>1</v>
@@ -116,10 +116,10 @@
     </row>
     <row r="3">
       <c r="A3" s="0">
-        <v>0.62454706561604656</v>
+        <v>0.066247503662573162</v>
       </c>
       <c r="B3" s="0">
-        <v>-0.7883866136351394</v>
+        <v>-0.084391060463968867</v>
       </c>
       <c r="C3" s="0">
         <v>3</v>
@@ -130,10 +130,10 @@
     </row>
     <row r="4">
       <c r="A4" s="0">
-        <v>0.78718107688061156</v>
+        <v>0.15161088794043498</v>
       </c>
       <c r="B4" s="0">
-        <v>0.32132530423390798</v>
+        <v>0.063060947738482393</v>
       </c>
       <c r="C4" s="0">
         <v>4</v>
@@ -144,10 +144,10 @@
     </row>
     <row r="5">
       <c r="A5" s="0">
-        <v>-0.21259871152943871</v>
+        <v>-0.060344327088798236</v>
       </c>
       <c r="B5" s="0">
-        <v>0.58656743148823942</v>
+        <v>0.15462717795987341</v>
       </c>
       <c r="C5" s="0">
         <v>5</v>
@@ -158,10 +158,10 @@
     </row>
     <row r="6">
       <c r="A6" s="0">
-        <v>-0.58166783399854682</v>
+        <v>-0.069393996904993288</v>
       </c>
       <c r="B6" s="0">
-        <v>-0.02456882853959555</v>
+        <v>-0.0018267462935495915</v>
       </c>
       <c r="C6" s="0">
         <v>6</v>
@@ -172,10 +172,10 @@
     </row>
     <row r="7">
       <c r="A7" s="0">
-        <v>-1.04209173764738</v>
+        <v>-0.20243234576482766</v>
       </c>
       <c r="B7" s="0">
-        <v>0.49077814687679422</v>
+        <v>0.10725985910707571</v>
       </c>
       <c r="C7" s="0">
         <v>8</v>
@@ -186,10 +186,10 @@
     </row>
     <row r="8">
       <c r="A8" s="0">
-        <v>-0.37214575272005351</v>
+        <v>-0.047250159216661369</v>
       </c>
       <c r="B8" s="0">
-        <v>2.2012123745458281</v>
+        <v>0.29473334129746587</v>
       </c>
       <c r="C8" s="0">
         <v>9</v>
@@ -200,10 +200,10 @@
     </row>
     <row r="9">
       <c r="A9" s="0">
-        <v>-1.6024522456460908</v>
+        <v>-0.20716118793311869</v>
       </c>
       <c r="B9" s="0">
-        <v>2.1514814841086864</v>
+        <v>0.27799948693191251</v>
       </c>
       <c r="C9" s="0">
         <v>10</v>
@@ -214,10 +214,10 @@
     </row>
     <row r="10">
       <c r="A10" s="0">
-        <v>-0.12772980820968236</v>
+        <v>-0.019397456107733094</v>
       </c>
       <c r="B10" s="0">
-        <v>1.319003504068607</v>
+        <v>0.20958718360881143</v>
       </c>
       <c r="C10" s="0">
         <v>11</v>
@@ -228,10 +228,10 @@
     </row>
     <row r="11">
       <c r="A11" s="0">
-        <v>-2.3452973740610821</v>
+        <v>-0.30655465164635815</v>
       </c>
       <c r="B11" s="0">
-        <v>0.73289814839415524</v>
+        <v>0.094994067911011587</v>
       </c>
       <c r="C11" s="0">
         <v>12</v>
@@ -242,10 +242,10 @@
     </row>
     <row r="12">
       <c r="A12" s="0">
-        <v>-0.69706540054011379</v>
+        <v>-0.10305652882038156</v>
       </c>
       <c r="B12" s="0">
-        <v>0.39581031522900895</v>
+        <v>0.065656044931736254</v>
       </c>
       <c r="C12" s="0">
         <v>13</v>
@@ -256,10 +256,10 @@
     </row>
     <row r="13">
       <c r="A13" s="0">
-        <v>0.46780779117659543</v>
+        <v>0.040519430941034662</v>
       </c>
       <c r="B13" s="0">
-        <v>0.22676411238634187</v>
+        <v>0.019454480913222494</v>
       </c>
       <c r="C13" s="0">
         <v>14</v>
@@ -270,10 +270,10 @@
     </row>
     <row r="14">
       <c r="A14" s="0">
-        <v>-0.30768634640554726</v>
+        <v>-0.027555871579263772</v>
       </c>
       <c r="B14" s="0">
-        <v>1.9962028209604967</v>
+        <v>0.17243094267058284</v>
       </c>
       <c r="C14" s="0">
         <v>16</v>
@@ -284,10 +284,10 @@
     </row>
     <row r="15">
       <c r="A15" s="0">
-        <v>-0.5086556203724999</v>
+        <v>-0.061865458117336847</v>
       </c>
       <c r="B15" s="0">
-        <v>-1.3119529975066326</v>
+        <v>-0.15392351276821661</v>
       </c>
       <c r="C15" s="0">
         <v>17</v>
@@ -298,10 +298,10 @@
     </row>
     <row r="16">
       <c r="A16" s="0">
-        <v>0.078077004740635919</v>
+        <v>-0.0036148273452045778</v>
       </c>
       <c r="B16" s="0">
-        <v>0.19490780138114444</v>
+        <v>0.018603921228772868</v>
       </c>
       <c r="C16" s="0">
         <v>18</v>
@@ -312,10 +312,10 @@
     </row>
     <row r="17">
       <c r="A17" s="0">
-        <v>-0.46926769646658462</v>
+        <v>-0.072288163472366759</v>
       </c>
       <c r="B17" s="0">
-        <v>0.49911784024900052</v>
+        <v>0.08109439583720976</v>
       </c>
       <c r="C17" s="0">
         <v>19</v>
@@ -326,10 +326,10 @@
     </row>
     <row r="18">
       <c r="A18" s="0">
-        <v>-1.6954831947217071</v>
+        <v>-0.28506422319486513</v>
       </c>
       <c r="B18" s="0">
-        <v>0.85608887710939019</v>
+        <v>0.14419888493830652</v>
       </c>
       <c r="C18" s="0">
         <v>20</v>
@@ -340,10 +340,10 @@
     </row>
     <row r="19">
       <c r="A19" s="0">
-        <v>-0.94343562952067839</v>
+        <v>-0.16454424771453766</v>
       </c>
       <c r="B19" s="0">
-        <v>-1.270306783270275</v>
+        <v>-0.21019466545548432</v>
       </c>
       <c r="C19" s="0">
         <v>21</v>
@@ -354,10 +354,10 @@
     </row>
     <row r="20">
       <c r="A20" s="0">
-        <v>1.0924430119272073</v>
+        <v>0.1126468433222326</v>
       </c>
       <c r="B20" s="0">
-        <v>-0.9076134768414591</v>
+        <v>-0.093437372666084456</v>
       </c>
       <c r="C20" s="0">
         <v>22</v>
@@ -368,10 +368,10 @@
     </row>
     <row r="21">
       <c r="A21" s="0">
-        <v>-1.5873417149653501</v>
+        <v>-0.24352850219326358</v>
       </c>
       <c r="B21" s="0">
-        <v>-0.59401134093422536</v>
+        <v>-0.093297461375905319</v>
       </c>
       <c r="C21" s="0">
         <v>23</v>
@@ -382,10 +382,10 @@
     </row>
     <row r="22">
       <c r="A22" s="0">
-        <v>-0.67989184002189318</v>
+        <v>-0.05425403169290835</v>
       </c>
       <c r="B22" s="0">
-        <v>0.71783661163560075</v>
+        <v>0.057110871783019254</v>
       </c>
       <c r="C22" s="0">
         <v>24</v>
@@ -396,10 +396,10 @@
     </row>
     <row r="23">
       <c r="A23" s="0">
-        <v>-0.3697385043880696</v>
+        <v>-0.067358598517878551</v>
       </c>
       <c r="B23" s="0">
-        <v>-0.075823412543528423</v>
+        <v>-0.010902311015032112</v>
       </c>
       <c r="C23" s="0">
         <v>25</v>
@@ -410,10 +410,10 @@
     </row>
     <row r="24">
       <c r="A24" s="0">
-        <v>-0.26783345209385939</v>
+        <v>-0.04728130048389062</v>
       </c>
       <c r="B24" s="0">
-        <v>-0.077960385151889744</v>
+        <v>0.33818693181767229</v>
       </c>
       <c r="C24" s="0">
         <v>26</v>
@@ -424,10 +424,10 @@
     </row>
     <row r="25">
       <c r="A25" s="0">
-        <v>-0.62185350859854383</v>
+        <v>-0.10738944760172325</v>
       </c>
       <c r="B25" s="0">
-        <v>-0.31460462027899905</v>
+        <v>-0.054795780540521991</v>
       </c>
       <c r="C25" s="0">
         <v>27</v>
@@ -438,10 +438,10 @@
     </row>
     <row r="26">
       <c r="A26" s="0">
-        <v>-0.65776425025342711</v>
+        <v>-0.12005090991432944</v>
       </c>
       <c r="B26" s="0">
-        <v>0.039452640370589806</v>
+        <v>0.010063744126109973</v>
       </c>
       <c r="C26" s="0">
         <v>28</v>
@@ -452,10 +452,10 @@
     </row>
     <row r="27">
       <c r="A27" s="0">
-        <v>-0.62827617972574223</v>
+        <v>-0.076198671847852534</v>
       </c>
       <c r="B27" s="0">
-        <v>-1.4619475989597075</v>
+        <v>-0.18117925084886383</v>
       </c>
       <c r="C27" s="0">
         <v>29</v>
@@ -466,10 +466,10 @@
     </row>
     <row r="28">
       <c r="A28" s="0">
-        <v>0.17395956107356406</v>
+        <v>0.045415125216444037</v>
       </c>
       <c r="B28" s="0">
-        <v>-1.0809807683656367</v>
+        <v>-0.28401231542960836</v>
       </c>
       <c r="C28" s="0">
         <v>30</v>
@@ -480,10 +480,10 @@
     </row>
     <row r="29">
       <c r="A29" s="0">
-        <v>-0.72442647738732757</v>
+        <v>-0.14016856717738999</v>
       </c>
       <c r="B29" s="0">
-        <v>1.1155537865695893</v>
+        <v>0.21591251470154973</v>
       </c>
       <c r="C29" s="0">
         <v>31</v>
@@ -494,10 +494,10 @@
     </row>
     <row r="30">
       <c r="A30" s="0">
-        <v>-0.78743571360536313</v>
+        <v>-0.077831757219351316</v>
       </c>
       <c r="B30" s="0">
-        <v>1.1229896375135073</v>
+        <v>0.11020093298569866</v>
       </c>
       <c r="C30" s="0">
         <v>32</v>
@@ -508,10 +508,10 @@
     </row>
     <row r="31">
       <c r="A31" s="0">
-        <v>-0.46298892096818023</v>
+        <v>-0.057811365990669369</v>
       </c>
       <c r="B31" s="0">
-        <v>-0.13817973798900413</v>
+        <v>-0.013803509463448743</v>
       </c>
       <c r="C31" s="0">
         <v>33</v>
@@ -522,10 +522,10 @@
     </row>
     <row r="32">
       <c r="A32" s="0">
-        <v>-0.90796144880128982</v>
+        <v>-0.12231779686325528</v>
       </c>
       <c r="B32" s="0">
-        <v>-0.49257767909156303</v>
+        <v>0.21755633220835613</v>
       </c>
       <c r="C32" s="0">
         <v>34</v>
@@ -565,10 +565,10 @@
     </row>
     <row r="2">
       <c r="A2" s="0">
-        <v>0.3116168696861894</v>
+        <v>0.31107761061287631</v>
       </c>
       <c r="B2" s="0">
-        <v>0.047840050050754757</v>
+        <v>0.033369328041358517</v>
       </c>
       <c r="C2" s="0">
         <v>1</v>
@@ -579,10 +579,10 @@
     </row>
     <row r="3">
       <c r="A3" s="0">
-        <v>0.15847859361480238</v>
+        <v>0.15850928323644833</v>
       </c>
       <c r="B3" s="0">
-        <v>0.028271276223757406</v>
+        <v>0.028364353592586385</v>
       </c>
       <c r="C3" s="0">
         <v>3</v>
@@ -593,10 +593,10 @@
     </row>
     <row r="4">
       <c r="A4" s="0">
-        <v>0.082898733623502266</v>
+        <v>0.082787930006776728</v>
       </c>
       <c r="B4" s="0">
-        <v>0.072014572747866615</v>
+        <v>0.071687147272185239</v>
       </c>
       <c r="C4" s="0">
         <v>4</v>
@@ -607,10 +607,10 @@
     </row>
     <row r="5">
       <c r="A5" s="0">
-        <v>0.06520300209161442</v>
+        <v>0.067059751460136707</v>
       </c>
       <c r="B5" s="0">
-        <v>0.034261611638144986</v>
+        <v>0.034633953950498869</v>
       </c>
       <c r="C5" s="0">
         <v>5</v>
@@ -621,10 +621,10 @@
     </row>
     <row r="6">
       <c r="A6" s="0">
-        <v>0.21261583130671444</v>
+        <v>0.21306576647367742</v>
       </c>
       <c r="B6" s="0">
-        <v>-0.076045904175957732</v>
+        <v>-0.076330415411074132</v>
       </c>
       <c r="C6" s="0">
         <v>6</v>
@@ -635,10 +635,10 @@
     </row>
     <row r="7">
       <c r="A7" s="0">
-        <v>-0.0056810140991333524</v>
+        <v>0.00040306734479977901</v>
       </c>
       <c r="B7" s="0">
-        <v>-0.056499871768278226</v>
+        <v>-0.059127494953807105</v>
       </c>
       <c r="C7" s="0">
         <v>8</v>
@@ -649,10 +649,10 @@
     </row>
     <row r="8">
       <c r="A8" s="0">
-        <v>-0.14070914821480116</v>
+        <v>-0.14044426365761933</v>
       </c>
       <c r="B8" s="0">
-        <v>-0.16383064874387404</v>
+        <v>-0.16497445590587756</v>
       </c>
       <c r="C8" s="0">
         <v>9</v>
@@ -663,10 +663,10 @@
     </row>
     <row r="9">
       <c r="A9" s="0">
-        <v>0.20657168918881064</v>
+        <v>0.20652468712216227</v>
       </c>
       <c r="B9" s="0">
-        <v>0.19872354496186131</v>
+        <v>0.19873249930884759</v>
       </c>
       <c r="C9" s="0">
         <v>10</v>
@@ -677,10 +677,10 @@
     </row>
     <row r="10">
       <c r="A10" s="0">
-        <v>-0.10724144517116579</v>
+        <v>-0.1081251876448061</v>
       </c>
       <c r="B10" s="0">
-        <v>0.039066510068830745</v>
+        <v>0.038611035464238809</v>
       </c>
       <c r="C10" s="0">
         <v>11</v>
@@ -691,10 +691,10 @@
     </row>
     <row r="11">
       <c r="A11" s="0">
-        <v>0.064161465947626783</v>
+        <v>0.064046084028943503</v>
       </c>
       <c r="B11" s="0">
-        <v>-0.045182784596742007</v>
+        <v>-0.044980764295198303</v>
       </c>
       <c r="C11" s="0">
         <v>12</v>
@@ -705,10 +705,10 @@
     </row>
     <row r="12">
       <c r="A12" s="0">
-        <v>0.032343371723298257</v>
+        <v>0.032063261065076287</v>
       </c>
       <c r="B12" s="0">
-        <v>-0.14511209752302512</v>
+        <v>-0.14515721300372153</v>
       </c>
       <c r="C12" s="0">
         <v>13</v>
@@ -719,10 +719,10 @@
     </row>
     <row r="13">
       <c r="A13" s="0">
-        <v>-0.063885942033317281</v>
+        <v>-0.06400756683183903</v>
       </c>
       <c r="B13" s="0">
-        <v>-0.40480575862936119</v>
+        <v>-0.4048679456139766</v>
       </c>
       <c r="C13" s="0">
         <v>14</v>
@@ -733,10 +733,10 @@
     </row>
     <row r="14">
       <c r="A14" s="0">
-        <v>-0.052823591498813841</v>
+        <v>-0.053046438812769298</v>
       </c>
       <c r="B14" s="0">
-        <v>0.091350128600143882</v>
+        <v>0.091719138472245221</v>
       </c>
       <c r="C14" s="0">
         <v>16</v>
@@ -747,10 +747,10 @@
     </row>
     <row r="15">
       <c r="A15" s="0">
-        <v>0.083359521908687201</v>
+        <v>0.083516999160908517</v>
       </c>
       <c r="B15" s="0">
-        <v>-0.097086338418018767</v>
+        <v>-0.097165629630445227</v>
       </c>
       <c r="C15" s="0">
         <v>17</v>
@@ -761,10 +761,10 @@
     </row>
     <row r="16">
       <c r="A16" s="0">
-        <v>0.27291790268060689</v>
+        <v>0.27067498469293544</v>
       </c>
       <c r="B16" s="0">
-        <v>0.24461775200152663</v>
+        <v>0.24514328329241456</v>
       </c>
       <c r="C16" s="0">
         <v>18</v>
@@ -775,10 +775,10 @@
     </row>
     <row r="17">
       <c r="A17" s="0">
-        <v>0.20045496630350179</v>
+        <v>0.20183981654253086</v>
       </c>
       <c r="B17" s="0">
-        <v>-0.12190461106661069</v>
+        <v>-0.12138347255246737</v>
       </c>
       <c r="C17" s="0">
         <v>19</v>
@@ -789,10 +789,10 @@
     </row>
     <row r="18">
       <c r="A18" s="0">
-        <v>0.018373230400179227</v>
+        <v>0.018429110377467854</v>
       </c>
       <c r="B18" s="0">
-        <v>-0.021138500995422412</v>
+        <v>-0.021411629133330598</v>
       </c>
       <c r="C18" s="0">
         <v>20</v>
@@ -803,10 +803,10 @@
     </row>
     <row r="19">
       <c r="A19" s="0">
-        <v>0.021743917946327067</v>
+        <v>0.024098736761843549</v>
       </c>
       <c r="B19" s="0">
-        <v>-0.022589848457734516</v>
+        <v>-0.021747489037077371</v>
       </c>
       <c r="C19" s="0">
         <v>21</v>
@@ -817,10 +817,10 @@
     </row>
     <row r="20">
       <c r="A20" s="0">
-        <v>-0.055572696746368243</v>
+        <v>-0.055625000450834669</v>
       </c>
       <c r="B20" s="0">
-        <v>-0.062708149791525697</v>
+        <v>-0.062766965624436871</v>
       </c>
       <c r="C20" s="0">
         <v>22</v>
@@ -831,10 +831,10 @@
     </row>
     <row r="21">
       <c r="A21" s="0">
-        <v>-0.043649341414669196</v>
+        <v>-0.044092009736333947</v>
       </c>
       <c r="B21" s="0">
-        <v>-0.052904319727810421</v>
+        <v>-0.053135643367119595</v>
       </c>
       <c r="C21" s="0">
         <v>23</v>
@@ -845,10 +845,10 @@
     </row>
     <row r="22">
       <c r="A22" s="0">
-        <v>-0.024906267399597455</v>
+        <v>-0.023871457183124244</v>
       </c>
       <c r="B22" s="0">
-        <v>-0.094346008341473789</v>
+        <v>-0.09498347738331854</v>
       </c>
       <c r="C22" s="0">
         <v>24</v>
@@ -859,10 +859,10 @@
     </row>
     <row r="23">
       <c r="A23" s="0">
-        <v>0.062428895847913252</v>
+        <v>0.061191799442943076</v>
       </c>
       <c r="B23" s="0">
-        <v>0.18917243164838835</v>
+        <v>0.18694720053104935</v>
       </c>
       <c r="C23" s="0">
         <v>25</v>
@@ -873,10 +873,10 @@
     </row>
     <row r="24">
       <c r="A24" s="0">
-        <v>0.012336877837265845</v>
+        <v>0.012392718304217362</v>
       </c>
       <c r="B24" s="0">
-        <v>0.010983394487947565</v>
+        <v>0.016266310459898833</v>
       </c>
       <c r="C24" s="0">
         <v>26</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="25">
       <c r="A25" s="0">
-        <v>0.049351209312066976</v>
+        <v>0.048107962694908725</v>
       </c>
       <c r="B25" s="0">
-        <v>0.09636388069166095</v>
+        <v>0.096179450808343656</v>
       </c>
       <c r="C25" s="0">
         <v>27</v>
@@ -901,10 +901,10 @@
     </row>
     <row r="26">
       <c r="A26" s="0">
-        <v>-0.19550448563364101</v>
+        <v>-0.19641802338490907</v>
       </c>
       <c r="B26" s="0">
-        <v>0.076404792518847658</v>
+        <v>0.075310561790422739</v>
       </c>
       <c r="C26" s="0">
         <v>28</v>
@@ -915,10 +915,10 @@
     </row>
     <row r="27">
       <c r="A27" s="0">
-        <v>0.32361518591297667</v>
+        <v>0.32371176655172834</v>
       </c>
       <c r="B27" s="0">
-        <v>-0.037206273835607324</v>
+        <v>-0.038150799197233382</v>
       </c>
       <c r="C27" s="0">
         <v>29</v>
@@ -929,10 +929,10 @@
     </row>
     <row r="28">
       <c r="A28" s="0">
-        <v>-0.13908686798763428</v>
+        <v>-0.13881748481114944</v>
       </c>
       <c r="B28" s="0">
-        <v>-0.12056492311655378</v>
+        <v>-0.12040040286183527</v>
       </c>
       <c r="C28" s="0">
         <v>30</v>
@@ -943,10 +943,10 @@
     </row>
     <row r="29">
       <c r="A29" s="0">
-        <v>-0.13891037720623403</v>
+        <v>-0.12035893332366832</v>
       </c>
       <c r="B29" s="0">
-        <v>-0.40929029296586378</v>
+        <v>-0.40926833717180666</v>
       </c>
       <c r="C29" s="0">
         <v>31</v>
@@ -957,10 +957,10 @@
     </row>
     <row r="30">
       <c r="A30" s="0">
-        <v>0.19011471892350171</v>
+        <v>0.19075762366890903</v>
       </c>
       <c r="B30" s="0">
-        <v>-0.075779029357253863</v>
+        <v>-0.076014038764302183</v>
       </c>
       <c r="C30" s="0">
         <v>32</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="31">
       <c r="A31" s="0">
-        <v>0.16798434421137493</v>
+        <v>0.16833832225719592</v>
       </c>
       <c r="B31" s="0">
-        <v>-0.09903379842968596</v>
+        <v>-0.099064697012763242</v>
       </c>
       <c r="C31" s="0">
         <v>33</v>
@@ -985,10 +985,10 @@
     </row>
     <row r="32">
       <c r="A32" s="0">
-        <v>0.2168764685115312</v>
+        <v>0.21706756042236827</v>
       </c>
       <c r="B32" s="0">
-        <v>0.19025214213167996</v>
+        <v>0.18951056729353705</v>
       </c>
       <c r="C32" s="0">
         <v>34</v>
